--- a/Examples/samples.xlsx
+++ b/Examples/samples.xlsx
@@ -8,27 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\pySAFER\Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AEF64F-7833-4019-B376-DCB2526CAE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1AC9FA-BDB7-4B5E-82BA-F46F62ED6C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40850" yWindow="2240" windowWidth="12220" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>data</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>lat</t>
   </si>
@@ -39,19 +47,16 @@
     <t>Tmin</t>
   </si>
   <si>
-    <t>rh</t>
+    <t>red</t>
   </si>
   <si>
-    <t>u2</t>
+    <t>nir</t>
   </si>
   <si>
-    <t>rs</t>
+    <t>date</t>
   </si>
   <si>
-    <t>ndvi</t>
-  </si>
-  <si>
-    <t>albedo</t>
+    <t>doy</t>
   </si>
 </sst>
 </file>
@@ -369,563 +374,743 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>20250501</v>
       </c>
       <c r="B2">
-        <v>37.365887999999998</v>
+        <v>121</v>
       </c>
       <c r="C2">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D2">
         <v>38</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>21.2</v>
       </c>
-      <c r="H2">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F2">
+        <v>0.03</v>
+      </c>
+      <c r="G2">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>20250502</v>
       </c>
       <c r="B3">
-        <v>37.365887999999998</v>
+        <v>122</v>
       </c>
       <c r="C3">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D3">
         <v>38.1</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>21.3</v>
       </c>
-      <c r="H3">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <v>0.03</v>
+      </c>
+      <c r="G3">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20250503</v>
       </c>
       <c r="B4">
-        <v>37.365887999999998</v>
+        <v>123</v>
       </c>
       <c r="C4">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D4">
         <v>38.200000000000003</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>21.4</v>
       </c>
-      <c r="H4">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F4">
+        <v>0.03</v>
+      </c>
+      <c r="G4">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20250504</v>
       </c>
       <c r="B5">
-        <v>37.365887999999998</v>
+        <v>124</v>
       </c>
       <c r="C5">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D5">
         <v>38.299999999999997</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>21.5</v>
       </c>
-      <c r="H5">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <v>0.03</v>
+      </c>
+      <c r="G5">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>20250505</v>
       </c>
       <c r="B6">
-        <v>37.365887999999998</v>
+        <v>125</v>
       </c>
       <c r="C6">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D6">
         <v>38.4</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>21.6</v>
       </c>
-      <c r="H6">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <v>0.03</v>
+      </c>
+      <c r="G6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>20250506</v>
       </c>
       <c r="B7">
-        <v>37.365887999999998</v>
+        <v>126</v>
       </c>
       <c r="C7">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D7">
         <v>38.5</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>21.7</v>
       </c>
-      <c r="H7">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F7">
+        <v>0.03</v>
+      </c>
+      <c r="G7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>20250507</v>
       </c>
       <c r="B8">
-        <v>37.365887999999998</v>
+        <v>127</v>
       </c>
       <c r="C8">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D8">
         <v>38.6</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>21.8</v>
       </c>
-      <c r="H8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F8">
+        <v>0.03</v>
+      </c>
+      <c r="G8">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>20250508</v>
       </c>
       <c r="B9">
-        <v>37.365887999999998</v>
+        <v>128</v>
       </c>
       <c r="C9">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D9">
         <v>38.700000000000003</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>21.9</v>
       </c>
-      <c r="H9">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F9">
+        <v>0.03</v>
+      </c>
+      <c r="G9">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>20250509</v>
       </c>
       <c r="B10">
-        <v>37.365887999999998</v>
+        <v>129</v>
       </c>
       <c r="C10">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D10">
         <v>38.799999999999997</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>22</v>
       </c>
-      <c r="H10">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F10">
+        <v>0.03</v>
+      </c>
+      <c r="G10">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>20250510</v>
       </c>
       <c r="B11">
-        <v>37.365887999999998</v>
+        <v>130</v>
       </c>
       <c r="C11">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D11">
         <v>38.9</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>22.1</v>
       </c>
-      <c r="H11">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F11">
+        <v>0.03</v>
+      </c>
+      <c r="G11">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>20250511</v>
       </c>
       <c r="B12">
-        <v>37.365887999999998</v>
+        <v>131</v>
       </c>
       <c r="C12">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D12">
         <v>39</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>22.2</v>
       </c>
-      <c r="H12">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <v>0.03</v>
+      </c>
+      <c r="G12">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>20250512</v>
       </c>
       <c r="B13">
-        <v>37.365887999999998</v>
+        <v>132</v>
       </c>
       <c r="C13">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D13">
         <v>39.1</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>22.3</v>
       </c>
-      <c r="H13">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F13">
+        <v>0.03</v>
+      </c>
+      <c r="G13">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>20250513</v>
       </c>
       <c r="B14">
-        <v>37.365887999999998</v>
+        <v>133</v>
       </c>
       <c r="C14">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D14">
         <v>39.200000000000003</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>22.4</v>
       </c>
-      <c r="H14">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F14">
+        <v>0.03</v>
+      </c>
+      <c r="G14">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>20250514</v>
       </c>
       <c r="B15">
-        <v>37.365887999999998</v>
+        <v>134</v>
       </c>
       <c r="C15">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D15">
         <v>39.299999999999997</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>22.5</v>
       </c>
-      <c r="H15">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F15">
+        <v>0.03</v>
+      </c>
+      <c r="G15">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>20250515</v>
       </c>
       <c r="B16">
-        <v>37.365887999999998</v>
+        <v>135</v>
       </c>
       <c r="C16">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D16">
         <v>39.4</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>22.6</v>
       </c>
-      <c r="H16">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F16">
+        <v>0.03</v>
+      </c>
+      <c r="G16">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>20250516</v>
       </c>
       <c r="B17">
-        <v>37.365887999999998</v>
+        <v>136</v>
       </c>
       <c r="C17">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D17">
         <v>39.5</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>22.7</v>
       </c>
-      <c r="H17">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F17">
+        <v>0.03</v>
+      </c>
+      <c r="G17">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>20250517</v>
       </c>
       <c r="B18">
-        <v>37.365887999999998</v>
+        <v>137</v>
       </c>
       <c r="C18">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D18">
         <v>39.6</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>22.8</v>
       </c>
-      <c r="H18">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F18">
+        <v>0.03</v>
+      </c>
+      <c r="G18">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>20250518</v>
       </c>
       <c r="B19">
-        <v>37.365887999999998</v>
+        <v>138</v>
       </c>
       <c r="C19">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D19">
         <v>39.700000000000003</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>22.9</v>
       </c>
-      <c r="H19">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F19">
+        <v>0.03</v>
+      </c>
+      <c r="G19">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>20250519</v>
       </c>
       <c r="B20">
-        <v>37.365887999999998</v>
+        <v>139</v>
       </c>
       <c r="C20">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D20">
         <v>39.799999999999997</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>23</v>
       </c>
-      <c r="H20">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F20">
+        <v>0.03</v>
+      </c>
+      <c r="G20">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20250520</v>
       </c>
       <c r="B21">
-        <v>37.365887999999998</v>
+        <v>140</v>
       </c>
       <c r="C21">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D21">
         <v>39.9</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>23.1</v>
       </c>
-      <c r="H21">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F21">
+        <v>0.03</v>
+      </c>
+      <c r="G21">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20250521</v>
       </c>
       <c r="B22">
-        <v>37.365887999999998</v>
+        <v>141</v>
       </c>
       <c r="C22">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D22">
         <v>40</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>23.2</v>
       </c>
-      <c r="H22">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F22">
+        <v>0.03</v>
+      </c>
+      <c r="G22">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20250522</v>
       </c>
       <c r="B23">
-        <v>37.365887999999998</v>
+        <v>142</v>
       </c>
       <c r="C23">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D23">
         <v>40.1</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>23.3</v>
       </c>
-      <c r="H23">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F23">
+        <v>0.03</v>
+      </c>
+      <c r="G23">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>20250523</v>
       </c>
       <c r="B24">
-        <v>37.365887999999998</v>
+        <v>143</v>
       </c>
       <c r="C24">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D24">
         <v>40.200000000000003</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>23.4</v>
       </c>
-      <c r="H24">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F24">
+        <v>0.03</v>
+      </c>
+      <c r="G24">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>20250524</v>
       </c>
       <c r="B25">
-        <v>37.365887999999998</v>
+        <v>144</v>
       </c>
       <c r="C25">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D25">
         <v>40.299999999999997</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>23.5</v>
       </c>
-      <c r="H25">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F25">
+        <v>0.03</v>
+      </c>
+      <c r="G25">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>20250525</v>
       </c>
       <c r="B26">
-        <v>37.365887999999998</v>
+        <v>145</v>
       </c>
       <c r="C26">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D26">
         <v>40.4</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>23.6</v>
       </c>
-      <c r="H26">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F26">
+        <v>0.03</v>
+      </c>
+      <c r="G26">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>20250526</v>
       </c>
       <c r="B27">
-        <v>37.365887999999998</v>
+        <v>146</v>
       </c>
       <c r="C27">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D27">
         <v>40.5</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <v>23.7</v>
       </c>
-      <c r="H27">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F27">
+        <v>0.03</v>
+      </c>
+      <c r="G27">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>20250527</v>
       </c>
       <c r="B28">
-        <v>37.365887999999998</v>
+        <v>147</v>
       </c>
       <c r="C28">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D28">
         <v>40.6</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <v>23.8</v>
       </c>
-      <c r="H28">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F28">
+        <v>0.03</v>
+      </c>
+      <c r="G28">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>20250528</v>
       </c>
       <c r="B29">
-        <v>37.365887999999998</v>
+        <v>148</v>
       </c>
       <c r="C29">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D29">
         <v>40.700000000000003</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <v>23.9</v>
       </c>
-      <c r="H29">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F29">
+        <v>0.03</v>
+      </c>
+      <c r="G29">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>20250529</v>
       </c>
       <c r="B30">
-        <v>37.365887999999998</v>
+        <v>149</v>
       </c>
       <c r="C30">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D30">
         <v>40.799999999999997</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <v>24</v>
       </c>
-      <c r="H30">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F30">
+        <v>0.03</v>
+      </c>
+      <c r="G30">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>20250530</v>
       </c>
       <c r="B31">
-        <v>37.365887999999998</v>
+        <v>150</v>
       </c>
       <c r="C31">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D31">
         <v>40.9</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <v>24.1</v>
       </c>
-      <c r="H31">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="F31">
+        <v>0.03</v>
+      </c>
+      <c r="G31">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>20250531</v>
       </c>
       <c r="B32">
-        <v>37.365887999999998</v>
+        <v>151</v>
       </c>
       <c r="C32">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="D32">
         <v>41</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <v>24.2</v>
       </c>
-      <c r="H32">
-        <v>0.85</v>
+      <c r="F32">
+        <v>0.03</v>
+      </c>
+      <c r="G32">
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>

--- a/Examples/samples.xlsx
+++ b/Examples/samples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\pySAFER\Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1AC9FA-BDB7-4B5E-82BA-F46F62ED6C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2542AC6D-CB83-4818-99A4-5034D8898875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40850" yWindow="2240" windowWidth="12220" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>lat</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>doy</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>eto</t>
   </si>
 </sst>
 </file>
@@ -374,743 +380,1080 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
       <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>20250501</v>
       </c>
       <c r="B2">
+        <v>2025</v>
+      </c>
+      <c r="C2">
         <v>121</v>
       </c>
-      <c r="C2">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D2">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E2">
         <v>38</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>21.2</v>
       </c>
-      <c r="F2">
-        <v>0.03</v>
-      </c>
       <c r="G2">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H2">
+        <v>0.36</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>20250502</v>
       </c>
       <c r="B3">
+        <v>2025</v>
+      </c>
+      <c r="C3">
         <v>122</v>
       </c>
-      <c r="C3">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D3">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E3">
         <v>38.1</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>21.3</v>
       </c>
-      <c r="F3">
-        <v>0.03</v>
-      </c>
       <c r="G3">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H3">
+        <v>0.36</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20250503</v>
       </c>
       <c r="B4">
+        <v>2025</v>
+      </c>
+      <c r="C4">
         <v>123</v>
       </c>
-      <c r="C4">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D4">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E4">
         <v>38.200000000000003</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>21.4</v>
       </c>
-      <c r="F4">
-        <v>0.03</v>
-      </c>
       <c r="G4">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H4">
+        <v>0.36</v>
+      </c>
+      <c r="I4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20250504</v>
       </c>
       <c r="B5">
+        <v>2025</v>
+      </c>
+      <c r="C5">
         <v>124</v>
       </c>
-      <c r="C5">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D5">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E5">
         <v>38.299999999999997</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>21.5</v>
       </c>
-      <c r="F5">
-        <v>0.03</v>
-      </c>
       <c r="G5">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H5">
+        <v>0.36</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>20250505</v>
       </c>
       <c r="B6">
+        <v>2025</v>
+      </c>
+      <c r="C6">
         <v>125</v>
       </c>
-      <c r="C6">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D6">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E6">
         <v>38.4</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>21.6</v>
       </c>
-      <c r="F6">
-        <v>0.03</v>
-      </c>
       <c r="G6">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H6">
+        <v>0.36</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>20250506</v>
       </c>
       <c r="B7">
+        <v>2025</v>
+      </c>
+      <c r="C7">
         <v>126</v>
       </c>
-      <c r="C7">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D7">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E7">
         <v>38.5</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>21.7</v>
       </c>
-      <c r="F7">
-        <v>0.03</v>
-      </c>
       <c r="G7">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H7">
+        <v>0.36</v>
+      </c>
+      <c r="I7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>20250507</v>
       </c>
       <c r="B8">
+        <v>2025</v>
+      </c>
+      <c r="C8">
         <v>127</v>
       </c>
-      <c r="C8">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D8">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E8">
         <v>38.6</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>21.8</v>
       </c>
-      <c r="F8">
-        <v>0.03</v>
-      </c>
       <c r="G8">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H8">
+        <v>0.36</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>20250508</v>
       </c>
       <c r="B9">
+        <v>2025</v>
+      </c>
+      <c r="C9">
         <v>128</v>
       </c>
-      <c r="C9">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D9">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E9">
         <v>38.700000000000003</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>21.9</v>
       </c>
-      <c r="F9">
-        <v>0.03</v>
-      </c>
       <c r="G9">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H9">
+        <v>0.36</v>
+      </c>
+      <c r="I9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>20250509</v>
       </c>
       <c r="B10">
+        <v>2025</v>
+      </c>
+      <c r="C10">
         <v>129</v>
       </c>
-      <c r="C10">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D10">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E10">
         <v>38.799999999999997</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>22</v>
       </c>
-      <c r="F10">
-        <v>0.03</v>
-      </c>
       <c r="G10">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H10">
+        <v>0.36</v>
+      </c>
+      <c r="I10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>20250510</v>
       </c>
       <c r="B11">
+        <v>2025</v>
+      </c>
+      <c r="C11">
         <v>130</v>
       </c>
-      <c r="C11">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D11">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E11">
         <v>38.9</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>22.1</v>
       </c>
-      <c r="F11">
-        <v>0.03</v>
-      </c>
       <c r="G11">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H11">
+        <v>0.36</v>
+      </c>
+      <c r="I11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>20250511</v>
       </c>
       <c r="B12">
+        <v>2025</v>
+      </c>
+      <c r="C12">
         <v>131</v>
       </c>
-      <c r="C12">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D12">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E12">
         <v>39</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>22.2</v>
       </c>
-      <c r="F12">
-        <v>0.03</v>
-      </c>
       <c r="G12">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H12">
+        <v>0.36</v>
+      </c>
+      <c r="I12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>20250512</v>
       </c>
       <c r="B13">
+        <v>2025</v>
+      </c>
+      <c r="C13">
         <v>132</v>
       </c>
-      <c r="C13">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D13">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E13">
         <v>39.1</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>22.3</v>
       </c>
-      <c r="F13">
-        <v>0.03</v>
-      </c>
       <c r="G13">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H13">
+        <v>0.36</v>
+      </c>
+      <c r="I13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>20250513</v>
       </c>
       <c r="B14">
+        <v>2025</v>
+      </c>
+      <c r="C14">
         <v>133</v>
       </c>
-      <c r="C14">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D14">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E14">
         <v>39.200000000000003</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>22.4</v>
       </c>
-      <c r="F14">
-        <v>0.03</v>
-      </c>
       <c r="G14">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H14">
+        <v>0.36</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>20250514</v>
       </c>
       <c r="B15">
+        <v>2025</v>
+      </c>
+      <c r="C15">
         <v>134</v>
       </c>
-      <c r="C15">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D15">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E15">
         <v>39.299999999999997</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>22.5</v>
       </c>
-      <c r="F15">
-        <v>0.03</v>
-      </c>
       <c r="G15">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H15">
+        <v>0.36</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>20250515</v>
       </c>
       <c r="B16">
+        <v>2025</v>
+      </c>
+      <c r="C16">
         <v>135</v>
       </c>
-      <c r="C16">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D16">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E16">
         <v>39.4</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>22.6</v>
       </c>
-      <c r="F16">
-        <v>0.03</v>
-      </c>
       <c r="G16">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H16">
+        <v>0.36</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>20250516</v>
       </c>
       <c r="B17">
+        <v>2025</v>
+      </c>
+      <c r="C17">
         <v>136</v>
       </c>
-      <c r="C17">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D17">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E17">
         <v>39.5</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>22.7</v>
       </c>
-      <c r="F17">
-        <v>0.03</v>
-      </c>
       <c r="G17">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H17">
+        <v>0.36</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>20250517</v>
       </c>
       <c r="B18">
+        <v>2025</v>
+      </c>
+      <c r="C18">
         <v>137</v>
       </c>
-      <c r="C18">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D18">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E18">
         <v>39.6</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>22.8</v>
       </c>
-      <c r="F18">
-        <v>0.03</v>
-      </c>
       <c r="G18">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H18">
+        <v>0.36</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>20250518</v>
       </c>
       <c r="B19">
+        <v>2025</v>
+      </c>
+      <c r="C19">
         <v>138</v>
       </c>
-      <c r="C19">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D19">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E19">
         <v>39.700000000000003</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>22.9</v>
       </c>
-      <c r="F19">
-        <v>0.03</v>
-      </c>
       <c r="G19">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H19">
+        <v>0.36</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>20250519</v>
       </c>
       <c r="B20">
+        <v>2025</v>
+      </c>
+      <c r="C20">
         <v>139</v>
       </c>
-      <c r="C20">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D20">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E20">
         <v>39.799999999999997</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>23</v>
       </c>
-      <c r="F20">
-        <v>0.03</v>
-      </c>
       <c r="G20">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H20">
+        <v>0.36</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20250520</v>
       </c>
       <c r="B21">
+        <v>2025</v>
+      </c>
+      <c r="C21">
         <v>140</v>
       </c>
-      <c r="C21">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D21">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E21">
         <v>39.9</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>23.1</v>
       </c>
-      <c r="F21">
-        <v>0.03</v>
-      </c>
       <c r="G21">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H21">
+        <v>0.36</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20250521</v>
       </c>
       <c r="B22">
+        <v>2025</v>
+      </c>
+      <c r="C22">
         <v>141</v>
       </c>
-      <c r="C22">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D22">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E22">
         <v>40</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>23.2</v>
       </c>
-      <c r="F22">
-        <v>0.03</v>
-      </c>
       <c r="G22">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H22">
+        <v>0.36</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20250522</v>
       </c>
       <c r="B23">
+        <v>2025</v>
+      </c>
+      <c r="C23">
         <v>142</v>
       </c>
-      <c r="C23">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D23">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E23">
         <v>40.1</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>23.3</v>
       </c>
-      <c r="F23">
-        <v>0.03</v>
-      </c>
       <c r="G23">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H23">
+        <v>0.36</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>20250523</v>
       </c>
       <c r="B24">
+        <v>2025</v>
+      </c>
+      <c r="C24">
         <v>143</v>
       </c>
-      <c r="C24">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D24">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E24">
         <v>40.200000000000003</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>23.4</v>
       </c>
-      <c r="F24">
-        <v>0.03</v>
-      </c>
       <c r="G24">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H24">
+        <v>0.36</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>20250524</v>
       </c>
       <c r="B25">
+        <v>2025</v>
+      </c>
+      <c r="C25">
         <v>144</v>
       </c>
-      <c r="C25">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D25">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E25">
         <v>40.299999999999997</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>23.5</v>
       </c>
-      <c r="F25">
-        <v>0.03</v>
-      </c>
       <c r="G25">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H25">
+        <v>0.36</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>20250525</v>
       </c>
       <c r="B26">
+        <v>2025</v>
+      </c>
+      <c r="C26">
         <v>145</v>
       </c>
-      <c r="C26">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D26">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E26">
         <v>40.4</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>23.6</v>
       </c>
-      <c r="F26">
-        <v>0.03</v>
-      </c>
       <c r="G26">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H26">
+        <v>0.36</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>20250526</v>
       </c>
       <c r="B27">
+        <v>2025</v>
+      </c>
+      <c r="C27">
         <v>146</v>
       </c>
-      <c r="C27">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D27">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E27">
         <v>40.5</v>
       </c>
-      <c r="E27">
+      <c r="F27">
         <v>23.7</v>
       </c>
-      <c r="F27">
-        <v>0.03</v>
-      </c>
       <c r="G27">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H27">
+        <v>0.36</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>20250527</v>
       </c>
       <c r="B28">
+        <v>2025</v>
+      </c>
+      <c r="C28">
         <v>147</v>
       </c>
-      <c r="C28">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D28">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E28">
         <v>40.6</v>
       </c>
-      <c r="E28">
+      <c r="F28">
         <v>23.8</v>
       </c>
-      <c r="F28">
-        <v>0.03</v>
-      </c>
       <c r="G28">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H28">
+        <v>0.36</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>20250528</v>
       </c>
       <c r="B29">
+        <v>2025</v>
+      </c>
+      <c r="C29">
         <v>148</v>
       </c>
-      <c r="C29">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D29">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E29">
         <v>40.700000000000003</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>23.9</v>
       </c>
-      <c r="F29">
-        <v>0.03</v>
-      </c>
       <c r="G29">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H29">
+        <v>0.36</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>20250529</v>
       </c>
       <c r="B30">
+        <v>2025</v>
+      </c>
+      <c r="C30">
         <v>149</v>
       </c>
-      <c r="C30">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D30">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E30">
         <v>40.799999999999997</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>24</v>
       </c>
-      <c r="F30">
-        <v>0.03</v>
-      </c>
       <c r="G30">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H30">
+        <v>0.36</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>20250530</v>
       </c>
       <c r="B31">
+        <v>2025</v>
+      </c>
+      <c r="C31">
         <v>150</v>
       </c>
-      <c r="C31">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D31">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E31">
         <v>40.9</v>
       </c>
-      <c r="E31">
+      <c r="F31">
         <v>24.1</v>
       </c>
-      <c r="F31">
-        <v>0.03</v>
-      </c>
       <c r="G31">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>0.03</v>
+      </c>
+      <c r="H31">
+        <v>0.36</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>20250531</v>
       </c>
       <c r="B32">
+        <v>2025</v>
+      </c>
+      <c r="C32">
         <v>151</v>
       </c>
-      <c r="C32">
-        <v>37.365887999999998</v>
-      </c>
       <c r="D32">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E32">
         <v>41</v>
       </c>
-      <c r="E32">
+      <c r="F32">
         <v>24.2</v>
       </c>
-      <c r="F32">
-        <v>0.03</v>
-      </c>
       <c r="G32">
-        <v>0.36</v>
+        <v>0.03</v>
+      </c>
+      <c r="H32">
+        <v>0.36</v>
+      </c>
+      <c r="I32">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>20250601</v>
+      </c>
+      <c r="B33">
+        <v>2025</v>
+      </c>
+      <c r="C33">
+        <v>151</v>
+      </c>
+      <c r="D33">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E33">
+        <v>41</v>
+      </c>
+      <c r="F33">
+        <v>24.2</v>
+      </c>
+      <c r="G33">
+        <v>0.15</v>
+      </c>
+      <c r="H33">
+        <v>0.12</v>
+      </c>
+      <c r="I33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>20250602</v>
+      </c>
+      <c r="B34">
+        <v>2025</v>
+      </c>
+      <c r="C34">
+        <v>151</v>
+      </c>
+      <c r="D34">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E34">
+        <v>41</v>
+      </c>
+      <c r="F34">
+        <v>24.2</v>
+      </c>
+      <c r="G34">
+        <v>0.15</v>
+      </c>
+      <c r="H34">
+        <v>0.12</v>
+      </c>
+      <c r="I34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35">
+        <v>20250603</v>
+      </c>
+      <c r="B35">
+        <v>2025</v>
+      </c>
+      <c r="C35">
+        <v>151</v>
+      </c>
+      <c r="D35">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E35">
+        <v>41</v>
+      </c>
+      <c r="F35">
+        <v>24.2</v>
+      </c>
+      <c r="G35">
+        <v>0.15</v>
+      </c>
+      <c r="H35">
+        <v>0.12</v>
+      </c>
+      <c r="I35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36">
+        <v>20250604</v>
+      </c>
+      <c r="B36">
+        <v>2025</v>
+      </c>
+      <c r="C36">
+        <v>151</v>
+      </c>
+      <c r="D36">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E36">
+        <v>41</v>
+      </c>
+      <c r="F36">
+        <v>24.2</v>
+      </c>
+      <c r="G36">
+        <v>0.15</v>
+      </c>
+      <c r="H36">
+        <v>0.12</v>
+      </c>
+      <c r="I36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A37">
+        <v>20250605</v>
+      </c>
+      <c r="B37">
+        <v>2025</v>
+      </c>
+      <c r="C37">
+        <v>151</v>
+      </c>
+      <c r="D37">
+        <v>37.365887999999998</v>
+      </c>
+      <c r="E37">
+        <v>41</v>
+      </c>
+      <c r="F37">
+        <v>24.2</v>
+      </c>
+      <c r="G37">
+        <v>0.15</v>
+      </c>
+      <c r="H37">
+        <v>0.12</v>
+      </c>
+      <c r="I37">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Examples/samples.xlsx
+++ b/Examples/samples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\pySAFER\Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2542AC6D-CB83-4818-99A4-5034D8898875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F0B030-F06A-4B24-8F0A-D451AEF63319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="40850" yWindow="2240" windowWidth="12220" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>lat</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>eto</t>
+  </si>
+  <si>
+    <t>elevation</t>
   </si>
 </sst>
 </file>
@@ -380,10 +383,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -411,8 +414,11 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>20250501</v>
       </c>
@@ -440,8 +446,11 @@
       <c r="I2">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>20250502</v>
       </c>
@@ -469,8 +478,11 @@
       <c r="I3">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20250503</v>
       </c>
@@ -498,8 +510,11 @@
       <c r="I4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20250504</v>
       </c>
@@ -527,8 +542,11 @@
       <c r="I5">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>20250505</v>
       </c>
@@ -556,8 +574,11 @@
       <c r="I6">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>20250506</v>
       </c>
@@ -585,8 +606,11 @@
       <c r="I7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>20250507</v>
       </c>
@@ -614,8 +638,11 @@
       <c r="I8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>20250508</v>
       </c>
@@ -643,8 +670,11 @@
       <c r="I9">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>20250509</v>
       </c>
@@ -672,8 +702,11 @@
       <c r="I10">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>20250510</v>
       </c>
@@ -701,8 +734,11 @@
       <c r="I11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>20250511</v>
       </c>
@@ -730,8 +766,11 @@
       <c r="I12">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>20250512</v>
       </c>
@@ -759,8 +798,11 @@
       <c r="I13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>20250513</v>
       </c>
@@ -788,8 +830,11 @@
       <c r="I14">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>20250514</v>
       </c>
@@ -817,8 +862,11 @@
       <c r="I15">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>20250515</v>
       </c>
@@ -846,8 +894,11 @@
       <c r="I16">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>20250516</v>
       </c>
@@ -875,8 +926,11 @@
       <c r="I17">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>20250517</v>
       </c>
@@ -904,8 +958,11 @@
       <c r="I18">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>20250518</v>
       </c>
@@ -933,8 +990,11 @@
       <c r="I19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>20250519</v>
       </c>
@@ -962,8 +1022,11 @@
       <c r="I20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J20">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20250520</v>
       </c>
@@ -991,8 +1054,11 @@
       <c r="I21">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20250521</v>
       </c>
@@ -1020,8 +1086,11 @@
       <c r="I22">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20250522</v>
       </c>
@@ -1049,8 +1118,11 @@
       <c r="I23">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J23">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>20250523</v>
       </c>
@@ -1078,8 +1150,11 @@
       <c r="I24">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J24">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>20250524</v>
       </c>
@@ -1107,8 +1182,11 @@
       <c r="I25">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>20250525</v>
       </c>
@@ -1136,8 +1214,11 @@
       <c r="I26">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J26">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>20250526</v>
       </c>
@@ -1165,8 +1246,11 @@
       <c r="I27">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J27">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>20250527</v>
       </c>
@@ -1194,8 +1278,11 @@
       <c r="I28">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J28">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>20250528</v>
       </c>
@@ -1223,8 +1310,11 @@
       <c r="I29">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J29">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>20250529</v>
       </c>
@@ -1252,8 +1342,11 @@
       <c r="I30">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J30">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>20250530</v>
       </c>
@@ -1281,8 +1374,11 @@
       <c r="I31">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J31">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>20250531</v>
       </c>
@@ -1310,8 +1406,11 @@
       <c r="I32">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J32">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>20250601</v>
       </c>
@@ -1339,8 +1438,11 @@
       <c r="I33">
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J33">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>20250602</v>
       </c>
@@ -1368,8 +1470,11 @@
       <c r="I34">
         <v>12</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J34">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>20250603</v>
       </c>
@@ -1397,8 +1502,11 @@
       <c r="I35">
         <v>12</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>20250604</v>
       </c>
@@ -1426,8 +1534,11 @@
       <c r="I36">
         <v>12</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J36">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>20250605</v>
       </c>
@@ -1454,6 +1565,9 @@
       </c>
       <c r="I37">
         <v>12</v>
+      </c>
+      <c r="J37">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Examples/samples.xlsx
+++ b/Examples/samples.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F0B030-F06A-4B24-8F0A-D451AEF63319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40850" yWindow="2240" windowWidth="12220" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="41180" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Examples/samples.xlsx
+++ b/Examples/samples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\pySAFER\Examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F0B030-F06A-4B24-8F0A-D451AEF63319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91679D8E-D357-46A5-9558-F6915B31CD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="41180" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>lat</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>year</t>
-  </si>
-  <si>
-    <t>eto</t>
   </si>
   <si>
     <t>elevation</t>
@@ -383,10 +380,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -414,11 +411,8 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>20250501</v>
       </c>
@@ -444,13 +438,10 @@
         <v>0.36</v>
       </c>
       <c r="I2">
-        <v>10</v>
-      </c>
-      <c r="J2">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>20250502</v>
       </c>
@@ -476,13 +467,10 @@
         <v>0.36</v>
       </c>
       <c r="I3">
-        <v>10</v>
-      </c>
-      <c r="J3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>20250503</v>
       </c>
@@ -508,13 +496,10 @@
         <v>0.36</v>
       </c>
       <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>20250504</v>
       </c>
@@ -540,13 +525,10 @@
         <v>0.36</v>
       </c>
       <c r="I5">
-        <v>10</v>
-      </c>
-      <c r="J5">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>20250505</v>
       </c>
@@ -572,13 +554,10 @@
         <v>0.36</v>
       </c>
       <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>20250506</v>
       </c>
@@ -604,13 +583,10 @@
         <v>0.36</v>
       </c>
       <c r="I7">
-        <v>10</v>
-      </c>
-      <c r="J7">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>20250507</v>
       </c>
@@ -636,13 +612,10 @@
         <v>0.36</v>
       </c>
       <c r="I8">
-        <v>10</v>
-      </c>
-      <c r="J8">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>20250508</v>
       </c>
@@ -668,13 +641,10 @@
         <v>0.36</v>
       </c>
       <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>20250509</v>
       </c>
@@ -700,13 +670,10 @@
         <v>0.36</v>
       </c>
       <c r="I10">
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>20250510</v>
       </c>
@@ -732,13 +699,10 @@
         <v>0.36</v>
       </c>
       <c r="I11">
-        <v>10</v>
-      </c>
-      <c r="J11">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>20250511</v>
       </c>
@@ -764,13 +728,10 @@
         <v>0.36</v>
       </c>
       <c r="I12">
-        <v>10</v>
-      </c>
-      <c r="J12">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>20250512</v>
       </c>
@@ -796,13 +757,10 @@
         <v>0.36</v>
       </c>
       <c r="I13">
-        <v>10</v>
-      </c>
-      <c r="J13">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>20250513</v>
       </c>
@@ -828,13 +786,10 @@
         <v>0.36</v>
       </c>
       <c r="I14">
-        <v>10</v>
-      </c>
-      <c r="J14">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>20250514</v>
       </c>
@@ -860,13 +815,10 @@
         <v>0.36</v>
       </c>
       <c r="I15">
-        <v>10</v>
-      </c>
-      <c r="J15">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>20250515</v>
       </c>
@@ -892,13 +844,10 @@
         <v>0.36</v>
       </c>
       <c r="I16">
-        <v>10</v>
-      </c>
-      <c r="J16">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>20250516</v>
       </c>
@@ -924,13 +873,10 @@
         <v>0.36</v>
       </c>
       <c r="I17">
-        <v>10</v>
-      </c>
-      <c r="J17">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>20250517</v>
       </c>
@@ -956,13 +902,10 @@
         <v>0.36</v>
       </c>
       <c r="I18">
-        <v>10</v>
-      </c>
-      <c r="J18">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>20250518</v>
       </c>
@@ -988,13 +931,10 @@
         <v>0.36</v>
       </c>
       <c r="I19">
-        <v>10</v>
-      </c>
-      <c r="J19">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>20250519</v>
       </c>
@@ -1020,13 +960,10 @@
         <v>0.36</v>
       </c>
       <c r="I20">
-        <v>10</v>
-      </c>
-      <c r="J20">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20250520</v>
       </c>
@@ -1052,13 +989,10 @@
         <v>0.36</v>
       </c>
       <c r="I21">
-        <v>10</v>
-      </c>
-      <c r="J21">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20250521</v>
       </c>
@@ -1084,13 +1018,10 @@
         <v>0.36</v>
       </c>
       <c r="I22">
-        <v>10</v>
-      </c>
-      <c r="J22">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>20250522</v>
       </c>
@@ -1116,13 +1047,10 @@
         <v>0.36</v>
       </c>
       <c r="I23">
-        <v>10</v>
-      </c>
-      <c r="J23">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>20250523</v>
       </c>
@@ -1148,13 +1076,10 @@
         <v>0.36</v>
       </c>
       <c r="I24">
-        <v>10</v>
-      </c>
-      <c r="J24">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>20250524</v>
       </c>
@@ -1180,13 +1105,10 @@
         <v>0.36</v>
       </c>
       <c r="I25">
-        <v>10</v>
-      </c>
-      <c r="J25">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>20250525</v>
       </c>
@@ -1212,13 +1134,10 @@
         <v>0.36</v>
       </c>
       <c r="I26">
-        <v>10</v>
-      </c>
-      <c r="J26">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>20250526</v>
       </c>
@@ -1244,13 +1163,10 @@
         <v>0.36</v>
       </c>
       <c r="I27">
-        <v>10</v>
-      </c>
-      <c r="J27">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>20250527</v>
       </c>
@@ -1276,13 +1192,10 @@
         <v>0.36</v>
       </c>
       <c r="I28">
-        <v>10</v>
-      </c>
-      <c r="J28">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>20250528</v>
       </c>
@@ -1308,13 +1221,10 @@
         <v>0.36</v>
       </c>
       <c r="I29">
-        <v>10</v>
-      </c>
-      <c r="J29">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>20250529</v>
       </c>
@@ -1340,13 +1250,10 @@
         <v>0.36</v>
       </c>
       <c r="I30">
-        <v>10</v>
-      </c>
-      <c r="J30">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>20250530</v>
       </c>
@@ -1372,13 +1279,10 @@
         <v>0.36</v>
       </c>
       <c r="I31">
-        <v>10</v>
-      </c>
-      <c r="J31">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>20250531</v>
       </c>
@@ -1404,13 +1308,10 @@
         <v>0.36</v>
       </c>
       <c r="I32">
-        <v>10</v>
-      </c>
-      <c r="J32">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>20250601</v>
       </c>
@@ -1436,13 +1337,10 @@
         <v>0.12</v>
       </c>
       <c r="I33">
-        <v>12</v>
-      </c>
-      <c r="J33">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>20250602</v>
       </c>
@@ -1468,13 +1366,10 @@
         <v>0.12</v>
       </c>
       <c r="I34">
-        <v>12</v>
-      </c>
-      <c r="J34">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>20250603</v>
       </c>
@@ -1500,13 +1395,10 @@
         <v>0.12</v>
       </c>
       <c r="I35">
-        <v>12</v>
-      </c>
-      <c r="J35">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>20250604</v>
       </c>
@@ -1532,13 +1424,10 @@
         <v>0.12</v>
       </c>
       <c r="I36">
-        <v>12</v>
-      </c>
-      <c r="J36">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>20250605</v>
       </c>
@@ -1564,9 +1453,6 @@
         <v>0.12</v>
       </c>
       <c r="I37">
-        <v>12</v>
-      </c>
-      <c r="J37">
         <v>65</v>
       </c>
     </row>
